--- a/testdata/LoginData.xlsx
+++ b/testdata/LoginData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanjana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CF7839F-CB68-4E60-B8D3-1640143474E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125F9649-81F6-4BA3-9131-156955055CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2F39C38C-548C-42BB-BA7B-98B30815A268}"/>
+    <workbookView xWindow="4068" yWindow="4044" windowWidth="17280" windowHeight="6876" xr2:uid="{2F39C38C-548C-42BB-BA7B-98B30815A268}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <t>Energy@2026</t>
   </si>
   <si>
-    <t>https://d2m63gufb5x623.cloudfront.net/login</t>
+    <t>https://qatest.sunscape.solar/login</t>
   </si>
 </sst>
 </file>
@@ -461,15 +461,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010022B4D0AA55F92E45BADEB46B4981431D" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fcf5fe5be6e45a339ddbd122f5b1547d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="89a830c3-6633-44dc-81b9-18b88b7337a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea82ac440927245935500796acadb08a" ns3:_="">
     <xsd:import namespace="89a830c3-6633-44dc-81b9-18b88b7337a8"/>
@@ -645,6 +636,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -654,14 +654,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9830C0F1-0B4C-49E5-8101-6D7522E4870D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33D60C4F-71E5-41FA-B580-3BDC4931E5E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -679,6 +671,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9830C0F1-0B4C-49E5-8101-6D7522E4870D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC27EFA4-A681-4D45-BCDF-F00A2871D59E}">
   <ds:schemaRefs>
